--- a/cadence-all+分工0817赵雷.xlsx
+++ b/cadence-all+分工0817赵雷.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\python_projects\testability_projects\extract_cadence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7254E49C-E162-4A1D-B474-7E4A810DDAA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDEDFFAC-D6FC-4C3F-A4A8-6692AD48F927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="540" windowWidth="16575" windowHeight="14310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3192" yWindow="0" windowWidth="11520" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
@@ -32,10 +32,20 @@
   <commentList>
     <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
-        <t>[线程批注]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="等线"/>
+            <family val="3"/>
+            <charset val="134"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[线程批注]
 你的Excel版本可读取此线程批注; 但如果在更新版本的Excel中打开文件，则对批注所作的任何改动都将被删除。了解详细信息: https://go.microsoft.com/fwlink/?linkid=870924
 注释:
     1.都应该包括文档来源（名称）、位置2.若未找到相关信息，请返回none</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -43,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="294">
   <si>
     <t>准则序号</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -1963,6 +1973,79 @@
 也是GND之间作比较 比较范围是同一层</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>get_positioning_hole_list</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>hole_id: 定位孔唯一标识符</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">​
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>diameter: 定位孔直径（mm）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">​
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>x_position: 定位孔中心点 X 坐标（mm）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">​
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>y_position: 定位孔中心点 Y 坐标（mm）</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2072,7 +2155,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2088,6 +2171,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2218,7 +2307,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2354,6 +2443,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2787,13 +2891,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表1" displayName="表1" ref="A1:H91" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9" totalsRowBorderDxfId="8" headerRowCellStyle="常规 3" dataCellStyle="常规 3">
-  <autoFilter ref="A1:H91" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="赵"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:H91" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="准则序号" dataDxfId="7" dataCellStyle="常规 3"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="类别" dataDxfId="6" dataCellStyle="常规 3"/>
@@ -2809,9 +2907,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2849,7 +2947,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2955,7 +3053,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3097,7 +3195,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3114,20 +3212,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H91"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.25" style="9" customWidth="1"/>
-    <col min="2" max="2" width="9.125" style="9"/>
-    <col min="3" max="3" width="30.25" style="9" customWidth="1"/>
+    <col min="1" max="1" width="10.21875" style="9" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="9"/>
+    <col min="3" max="3" width="30.21875" style="9" customWidth="1"/>
     <col min="4" max="4" width="8" style="9" customWidth="1"/>
-    <col min="5" max="5" width="34.75" style="19" customWidth="1"/>
-    <col min="6" max="6" width="24.75" style="9" customWidth="1"/>
-    <col min="7" max="7" width="43.75" style="9" customWidth="1"/>
-    <col min="8" max="8" width="83.25" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.125" style="9"/>
+    <col min="5" max="5" width="34.77734375" style="19" customWidth="1"/>
+    <col min="6" max="6" width="24.77734375" style="9" customWidth="1"/>
+    <col min="7" max="7" width="43.77734375" style="9" customWidth="1"/>
+    <col min="8" max="8" width="83.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.109375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
@@ -3153,7 +3251,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="82.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="124.8" x14ac:dyDescent="0.25">
       <c r="A2" s="20">
         <v>21</v>
       </c>
@@ -3177,7 +3275,7 @@
       </c>
       <c r="H2" s="38"/>
     </row>
-    <row r="3" spans="1:8" ht="99" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="124.8" x14ac:dyDescent="0.25">
       <c r="A3" s="20">
         <v>21</v>
       </c>
@@ -3201,7 +3299,7 @@
       </c>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8" ht="165" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="202.8" x14ac:dyDescent="0.25">
       <c r="A4" s="20">
         <v>21</v>
       </c>
@@ -3225,7 +3323,7 @@
       </c>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="148.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="171.6" x14ac:dyDescent="0.25">
       <c r="A5" s="20">
         <v>21</v>
       </c>
@@ -3249,7 +3347,7 @@
       </c>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8" ht="82.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="124.8" x14ac:dyDescent="0.25">
       <c r="A6" s="21">
         <v>22</v>
       </c>
@@ -3271,7 +3369,7 @@
       </c>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:8" ht="66" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="62.4" x14ac:dyDescent="0.25">
       <c r="A7" s="21">
         <v>22</v>
       </c>
@@ -3295,7 +3393,7 @@
       </c>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="1:8" ht="82.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="124.8" x14ac:dyDescent="0.25">
       <c r="A8" s="21">
         <v>22</v>
       </c>
@@ -3319,7 +3417,7 @@
       </c>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8" ht="99" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="124.8" x14ac:dyDescent="0.25">
       <c r="A9" s="21">
         <v>22</v>
       </c>
@@ -3343,7 +3441,7 @@
       </c>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8" ht="115.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="187.2" x14ac:dyDescent="0.25">
       <c r="A10" s="21">
         <v>22</v>
       </c>
@@ -3367,7 +3465,7 @@
       </c>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:8" ht="264" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="265.2" x14ac:dyDescent="0.25">
       <c r="A11" s="39">
         <v>25</v>
       </c>
@@ -3393,7 +3491,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="115.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="109.2" x14ac:dyDescent="0.25">
       <c r="A12" s="39">
         <v>25</v>
       </c>
@@ -3419,7 +3517,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="99" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="93.6" x14ac:dyDescent="0.25">
       <c r="A13" s="20">
         <v>25</v>
       </c>
@@ -3445,7 +3543,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="99" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="93.6" x14ac:dyDescent="0.25">
       <c r="A14" s="20">
         <v>25</v>
       </c>
@@ -3471,7 +3569,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="409.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A15" s="20">
         <v>26</v>
       </c>
@@ -3495,7 +3593,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:8" ht="409.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A16" s="20">
         <v>26</v>
       </c>
@@ -3519,7 +3617,7 @@
       </c>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="1:8" ht="409.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" ht="390" x14ac:dyDescent="0.25">
       <c r="A17" s="20">
         <v>26</v>
       </c>
@@ -3543,7 +3641,7 @@
       </c>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8" ht="396" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" ht="374.4" x14ac:dyDescent="0.25">
       <c r="A18" s="20">
         <v>26</v>
       </c>
@@ -3567,7 +3665,7 @@
       </c>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8" ht="313.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" ht="312" x14ac:dyDescent="0.25">
       <c r="A19" s="20">
         <v>26</v>
       </c>
@@ -3591,7 +3689,7 @@
       </c>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8" ht="231" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" ht="218.4" x14ac:dyDescent="0.25">
       <c r="A20" s="22">
         <v>27</v>
       </c>
@@ -3617,7 +3715,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="247.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" ht="265.2" x14ac:dyDescent="0.25">
       <c r="A21" s="22">
         <v>27</v>
       </c>
@@ -3641,7 +3739,7 @@
       </c>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="1:8" ht="396" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" ht="405.6" x14ac:dyDescent="0.25">
       <c r="A22" s="22">
         <v>27</v>
       </c>
@@ -3665,7 +3763,7 @@
       </c>
       <c r="H22" s="3"/>
     </row>
-    <row r="23" spans="1:8" ht="409.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A23" s="22">
         <v>27</v>
       </c>
@@ -3689,7 +3787,7 @@
       </c>
       <c r="H23" s="3"/>
     </row>
-    <row r="24" spans="1:8" ht="148.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" ht="187.2" x14ac:dyDescent="0.25">
       <c r="A24" s="22">
         <v>27</v>
       </c>
@@ -3713,7 +3811,7 @@
       </c>
       <c r="H24" s="3"/>
     </row>
-    <row r="25" spans="1:8" ht="99" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" ht="93.6" x14ac:dyDescent="0.25">
       <c r="A25" s="20">
         <v>28</v>
       </c>
@@ -3735,7 +3833,7 @@
       </c>
       <c r="H25" s="3"/>
     </row>
-    <row r="26" spans="1:8" ht="49.5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" ht="46.8" x14ac:dyDescent="0.25">
       <c r="A26" s="20">
         <v>28</v>
       </c>
@@ -3761,7 +3859,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="66" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" ht="93.6" x14ac:dyDescent="0.25">
       <c r="A27" s="20">
         <v>28</v>
       </c>
@@ -3783,7 +3881,7 @@
       </c>
       <c r="H27" s="3"/>
     </row>
-    <row r="28" spans="1:8" ht="66" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" ht="109.2" x14ac:dyDescent="0.25">
       <c r="A28" s="20">
         <v>28</v>
       </c>
@@ -3805,7 +3903,7 @@
       </c>
       <c r="H28" s="3"/>
     </row>
-    <row r="29" spans="1:8" ht="33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A29" s="23">
         <v>29</v>
       </c>
@@ -3827,7 +3925,7 @@
       <c r="G29" s="27"/>
       <c r="H29" s="3"/>
     </row>
-    <row r="30" spans="1:8" ht="49.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" ht="46.8" x14ac:dyDescent="0.25">
       <c r="A30" s="23">
         <v>29</v>
       </c>
@@ -3851,7 +3949,7 @@
       </c>
       <c r="H30" s="3"/>
     </row>
-    <row r="31" spans="1:8" ht="66" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" ht="62.4" x14ac:dyDescent="0.25">
       <c r="A31" s="23">
         <v>29</v>
       </c>
@@ -3875,7 +3973,7 @@
       </c>
       <c r="H31" s="3"/>
     </row>
-    <row r="32" spans="1:8" ht="82.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" ht="93.6" x14ac:dyDescent="0.25">
       <c r="A32" s="20">
         <v>30</v>
       </c>
@@ -3897,7 +3995,7 @@
       </c>
       <c r="H32" s="3"/>
     </row>
-    <row r="33" spans="1:8" ht="82.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" ht="93.6" x14ac:dyDescent="0.25">
       <c r="A33" s="20">
         <v>30</v>
       </c>
@@ -3919,7 +4017,7 @@
       </c>
       <c r="H33" s="3"/>
     </row>
-    <row r="34" spans="1:8" ht="409.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A34" s="20">
         <v>31</v>
       </c>
@@ -3943,7 +4041,7 @@
       </c>
       <c r="H34" s="3"/>
     </row>
-    <row r="35" spans="1:8" ht="379.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" ht="374.4" x14ac:dyDescent="0.25">
       <c r="A35" s="20">
         <v>31</v>
       </c>
@@ -3967,7 +4065,7 @@
       </c>
       <c r="H35" s="3"/>
     </row>
-    <row r="36" spans="1:8" ht="409.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A36" s="20">
         <v>31</v>
       </c>
@@ -3991,7 +4089,7 @@
       </c>
       <c r="H36" s="3"/>
     </row>
-    <row r="37" spans="1:8" ht="99" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" ht="140.4" x14ac:dyDescent="0.25">
       <c r="A37" s="20">
         <v>31</v>
       </c>
@@ -4011,7 +4109,7 @@
       </c>
       <c r="H37" s="3"/>
     </row>
-    <row r="38" spans="1:8" ht="148.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" ht="156" x14ac:dyDescent="0.25">
       <c r="A38" s="20">
         <v>31</v>
       </c>
@@ -4033,7 +4131,7 @@
       </c>
       <c r="H38" s="3"/>
     </row>
-    <row r="39" spans="1:8" ht="33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A39" s="20">
         <v>32</v>
       </c>
@@ -4055,7 +4153,7 @@
       <c r="G39" s="29"/>
       <c r="H39" s="3"/>
     </row>
-    <row r="40" spans="1:8" ht="82.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" ht="124.8" x14ac:dyDescent="0.25">
       <c r="A40" s="20">
         <v>32</v>
       </c>
@@ -4079,7 +4177,7 @@
       </c>
       <c r="H40" s="3"/>
     </row>
-    <row r="41" spans="1:8" ht="66" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" ht="62.4" x14ac:dyDescent="0.25">
       <c r="A41" s="20">
         <v>32</v>
       </c>
@@ -4103,7 +4201,7 @@
       </c>
       <c r="H41" s="3"/>
     </row>
-    <row r="42" spans="1:8" ht="33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A42" s="20">
         <v>33</v>
       </c>
@@ -4127,7 +4225,7 @@
       </c>
       <c r="H42" s="3"/>
     </row>
-    <row r="43" spans="1:8" ht="33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A43" s="20">
         <v>33</v>
       </c>
@@ -4149,7 +4247,7 @@
       <c r="G43" s="24"/>
       <c r="H43" s="3"/>
     </row>
-    <row r="44" spans="1:8" ht="33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" ht="46.8" x14ac:dyDescent="0.25">
       <c r="A44" s="20">
         <v>33</v>
       </c>
@@ -4173,7 +4271,7 @@
       </c>
       <c r="H44" s="3"/>
     </row>
-    <row r="45" spans="1:8" ht="33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A45" s="20">
         <v>33</v>
       </c>
@@ -4195,7 +4293,7 @@
       <c r="G45" s="24"/>
       <c r="H45" s="3"/>
     </row>
-    <row r="46" spans="1:8" ht="33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A46" s="20">
         <v>34</v>
       </c>
@@ -4217,7 +4315,7 @@
       <c r="G46" s="24"/>
       <c r="H46" s="3"/>
     </row>
-    <row r="47" spans="1:8" ht="132" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" ht="140.4" x14ac:dyDescent="0.25">
       <c r="A47" s="20">
         <v>34</v>
       </c>
@@ -4241,7 +4339,7 @@
       </c>
       <c r="H47" s="3"/>
     </row>
-    <row r="48" spans="1:8" ht="198" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" ht="187.2" x14ac:dyDescent="0.25">
       <c r="A48" s="20">
         <v>34</v>
       </c>
@@ -4265,7 +4363,7 @@
       </c>
       <c r="H48" s="3"/>
     </row>
-    <row r="49" spans="1:8" ht="66" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" ht="62.4" x14ac:dyDescent="0.25">
       <c r="A49" s="20">
         <v>34</v>
       </c>
@@ -4289,7 +4387,7 @@
       </c>
       <c r="H49" s="3"/>
     </row>
-    <row r="50" spans="1:8" ht="181.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" ht="171.6" x14ac:dyDescent="0.25">
       <c r="A50" s="20">
         <v>34</v>
       </c>
@@ -4313,7 +4411,7 @@
       </c>
       <c r="H50" s="3"/>
     </row>
-    <row r="51" spans="1:8" ht="33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A51" s="20">
         <v>35</v>
       </c>
@@ -4335,7 +4433,7 @@
       <c r="G51" s="29"/>
       <c r="H51" s="3"/>
     </row>
-    <row r="52" spans="1:8" ht="82.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" ht="78" x14ac:dyDescent="0.25">
       <c r="A52" s="20">
         <v>35</v>
       </c>
@@ -4359,7 +4457,7 @@
       </c>
       <c r="H52" s="3"/>
     </row>
-    <row r="53" spans="1:8" ht="82.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" ht="78" x14ac:dyDescent="0.25">
       <c r="A53" s="20">
         <v>35</v>
       </c>
@@ -4383,7 +4481,7 @@
       </c>
       <c r="H53" s="3"/>
     </row>
-    <row r="54" spans="1:8" ht="82.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" ht="124.8" x14ac:dyDescent="0.25">
       <c r="A54" s="20">
         <v>36</v>
       </c>
@@ -4405,7 +4503,7 @@
       </c>
       <c r="H54" s="3"/>
     </row>
-    <row r="55" spans="1:8" ht="99" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" ht="124.8" x14ac:dyDescent="0.25">
       <c r="A55" s="20">
         <v>36</v>
       </c>
@@ -4427,7 +4525,7 @@
       </c>
       <c r="H55" s="3"/>
     </row>
-    <row r="56" spans="1:8" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A56" s="20">
         <v>36</v>
       </c>
@@ -4447,7 +4545,7 @@
       <c r="G56" s="24"/>
       <c r="H56" s="3"/>
     </row>
-    <row r="57" spans="1:8" ht="148.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" ht="171.6" x14ac:dyDescent="0.25">
       <c r="A57" s="20">
         <v>36</v>
       </c>
@@ -4469,7 +4567,7 @@
       </c>
       <c r="H57" s="3"/>
     </row>
-    <row r="58" spans="1:8" ht="33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A58" s="20">
         <v>37</v>
       </c>
@@ -4491,7 +4589,7 @@
       <c r="G58" s="29"/>
       <c r="H58" s="3"/>
     </row>
-    <row r="59" spans="1:8" ht="82.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" ht="78" x14ac:dyDescent="0.25">
       <c r="A59" s="20">
         <v>37</v>
       </c>
@@ -4515,7 +4613,7 @@
       </c>
       <c r="H59" s="3"/>
     </row>
-    <row r="60" spans="1:8" ht="82.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" ht="78" x14ac:dyDescent="0.25">
       <c r="A60" s="20">
         <v>37</v>
       </c>
@@ -4539,7 +4637,7 @@
       </c>
       <c r="H60" s="3"/>
     </row>
-    <row r="61" spans="1:8" ht="82.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" ht="124.8" x14ac:dyDescent="0.25">
       <c r="A61" s="20">
         <v>38</v>
       </c>
@@ -4561,7 +4659,7 @@
       </c>
       <c r="H61" s="3"/>
     </row>
-    <row r="62" spans="1:8" ht="132" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" ht="124.8" x14ac:dyDescent="0.25">
       <c r="A62" s="44">
         <v>38</v>
       </c>
@@ -4587,7 +4685,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A63" s="20">
         <v>38</v>
       </c>
@@ -4607,7 +4705,7 @@
       <c r="G63" s="29"/>
       <c r="H63" s="3"/>
     </row>
-    <row r="64" spans="1:8" ht="66" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" ht="78" x14ac:dyDescent="0.25">
       <c r="A64" s="20">
         <v>39</v>
       </c>
@@ -4624,16 +4722,16 @@
         <v>274</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>173</v>
+        <v>292</v>
       </c>
       <c r="G64" s="24" t="s">
-        <v>174</v>
+        <v>293</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="66" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" ht="62.4" x14ac:dyDescent="0.25">
       <c r="A65" s="20">
         <v>39</v>
       </c>
@@ -4657,7 +4755,7 @@
       </c>
       <c r="H65" s="3"/>
     </row>
-    <row r="66" spans="1:8" ht="99" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" ht="93.6" x14ac:dyDescent="0.25">
       <c r="A66" s="20">
         <v>39</v>
       </c>
@@ -4681,7 +4779,7 @@
       </c>
       <c r="H66" s="3"/>
     </row>
-    <row r="67" spans="1:8" ht="409.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A67" s="20">
         <v>39</v>
       </c>
@@ -4705,7 +4803,7 @@
       </c>
       <c r="H67" s="3"/>
     </row>
-    <row r="68" spans="1:8" ht="33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A68" s="20">
         <v>40</v>
       </c>
@@ -4727,7 +4825,7 @@
       <c r="G68" s="29"/>
       <c r="H68" s="3"/>
     </row>
-    <row r="69" spans="1:8" ht="264" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" ht="265.2" x14ac:dyDescent="0.25">
       <c r="A69" s="20">
         <v>40</v>
       </c>
@@ -4751,7 +4849,7 @@
       </c>
       <c r="H69" s="3"/>
     </row>
-    <row r="70" spans="1:8" ht="409.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A70" s="20">
         <v>40</v>
       </c>
@@ -4775,7 +4873,7 @@
       </c>
       <c r="H70" s="3"/>
     </row>
-    <row r="71" spans="1:8" ht="330" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" ht="312" x14ac:dyDescent="0.25">
       <c r="A71" s="20">
         <v>40</v>
       </c>
@@ -4799,7 +4897,7 @@
       </c>
       <c r="H71" s="3"/>
     </row>
-    <row r="72" spans="1:8" ht="115.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" ht="156" x14ac:dyDescent="0.25">
       <c r="A72" s="20">
         <v>40</v>
       </c>
@@ -4823,7 +4921,7 @@
       </c>
       <c r="H72" s="3"/>
     </row>
-    <row r="73" spans="1:8" ht="33" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A73" s="20">
         <v>41</v>
       </c>
@@ -4845,31 +4943,31 @@
       <c r="G73" s="29"/>
       <c r="H73" s="3"/>
     </row>
-    <row r="74" spans="1:8" ht="82.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="20">
+    <row r="74" spans="1:8" ht="93.6" x14ac:dyDescent="0.25">
+      <c r="A74" s="48">
         <v>41</v>
       </c>
-      <c r="B74" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C74" s="3" t="s">
+      <c r="B74" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="C74" s="50" t="s">
         <v>203</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="D74" s="49" t="s">
         <v>268</v>
       </c>
-      <c r="E74" s="3" t="s">
+      <c r="E74" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="F74" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="G74" s="24" t="s">
+      <c r="G74" s="47" t="s">
         <v>204</v>
       </c>
-      <c r="H74" s="3"/>
-    </row>
-    <row r="75" spans="1:8" ht="66" x14ac:dyDescent="0.2">
+      <c r="H74" s="50"/>
+    </row>
+    <row r="75" spans="1:8" ht="62.4" x14ac:dyDescent="0.25">
       <c r="A75" s="20">
         <v>41</v>
       </c>
@@ -4895,7 +4993,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="66" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" ht="62.4" x14ac:dyDescent="0.25">
       <c r="A76" s="20">
         <v>41</v>
       </c>
@@ -4919,7 +5017,7 @@
       </c>
       <c r="H76" s="3"/>
     </row>
-    <row r="77" spans="1:8" ht="132" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" ht="140.4" x14ac:dyDescent="0.25">
       <c r="A77" s="20">
         <v>41</v>
       </c>
@@ -4943,7 +5041,7 @@
       </c>
       <c r="H77" s="3"/>
     </row>
-    <row r="78" spans="1:8" ht="231" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" ht="218.4" x14ac:dyDescent="0.25">
       <c r="A78" s="20">
         <v>41</v>
       </c>
@@ -4967,7 +5065,7 @@
       </c>
       <c r="H78" s="3"/>
     </row>
-    <row r="79" spans="1:8" ht="132" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" ht="124.8" x14ac:dyDescent="0.25">
       <c r="A79" s="20">
         <v>41</v>
       </c>
@@ -4991,7 +5089,7 @@
       </c>
       <c r="H79" s="3"/>
     </row>
-    <row r="80" spans="1:8" ht="99" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" ht="93.6" x14ac:dyDescent="0.25">
       <c r="A80" s="20">
         <v>41</v>
       </c>
@@ -5015,7 +5113,7 @@
       </c>
       <c r="H80" s="3"/>
     </row>
-    <row r="81" spans="1:8" ht="132" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:8" ht="124.8" x14ac:dyDescent="0.25">
       <c r="A81" s="20">
         <v>41</v>
       </c>
@@ -5039,7 +5137,7 @@
       </c>
       <c r="H81" s="3"/>
     </row>
-    <row r="82" spans="1:8" ht="82.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" ht="78" x14ac:dyDescent="0.25">
       <c r="A82" s="20">
         <v>42</v>
       </c>
@@ -5061,7 +5159,7 @@
       </c>
       <c r="H82" s="3"/>
     </row>
-    <row r="83" spans="1:8" ht="66" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8" ht="78" x14ac:dyDescent="0.25">
       <c r="A83" s="20">
         <v>42</v>
       </c>
@@ -5083,7 +5181,7 @@
       </c>
       <c r="H83" s="3"/>
     </row>
-    <row r="84" spans="1:8" ht="99" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" ht="109.2" x14ac:dyDescent="0.25">
       <c r="A84" s="20">
         <v>42</v>
       </c>
@@ -5107,7 +5205,7 @@
       </c>
       <c r="H84" s="3"/>
     </row>
-    <row r="85" spans="1:8" ht="181.5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" ht="202.8" x14ac:dyDescent="0.25">
       <c r="A85" s="39">
         <v>43</v>
       </c>
@@ -5133,7 +5231,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="99" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" ht="93.6" x14ac:dyDescent="0.25">
       <c r="A86" s="20">
         <v>43</v>
       </c>
@@ -5157,7 +5255,7 @@
       </c>
       <c r="H86" s="3"/>
     </row>
-    <row r="87" spans="1:8" ht="132" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" ht="140.4" x14ac:dyDescent="0.25">
       <c r="A87" s="20">
         <v>43</v>
       </c>
@@ -5181,7 +5279,7 @@
       </c>
       <c r="H87" s="3"/>
     </row>
-    <row r="88" spans="1:8" ht="115.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" ht="124.8" x14ac:dyDescent="0.25">
       <c r="A88" s="20">
         <v>43</v>
       </c>
@@ -5205,7 +5303,7 @@
       </c>
       <c r="H88" s="3"/>
     </row>
-    <row r="89" spans="1:8" ht="165" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" ht="156" x14ac:dyDescent="0.25">
       <c r="A89" s="20">
         <v>46</v>
       </c>
@@ -5229,7 +5327,7 @@
       </c>
       <c r="H89" s="3"/>
     </row>
-    <row r="90" spans="1:8" ht="396" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" ht="374.4" x14ac:dyDescent="0.25">
       <c r="A90" s="20">
         <v>46</v>
       </c>
@@ -5253,7 +5351,7 @@
       </c>
       <c r="H90" s="3"/>
     </row>
-    <row r="91" spans="1:8" ht="409.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A91" s="33">
         <v>46</v>
       </c>
